--- a/artfynd/A 46932-2020 artfynd.xlsx
+++ b/artfynd/A 46932-2020 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123158428</v>
+        <v>123158425</v>
       </c>
       <c r="B2" t="n">
         <v>58336</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>440508</v>
+        <v>440504</v>
       </c>
       <c r="R2" t="n">
-        <v>6511917</v>
+        <v>6511909</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123158425</v>
+        <v>123158428</v>
       </c>
       <c r="B3" t="n">
         <v>58336</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>440504</v>
+        <v>440508</v>
       </c>
       <c r="R3" t="n">
-        <v>6511909</v>
+        <v>6511917</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -879,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123158448</v>
+        <v>123158427</v>
       </c>
       <c r="B4" t="n">
         <v>58336</v>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>440528</v>
+        <v>440503</v>
       </c>
       <c r="R4" t="n">
-        <v>6511918</v>
+        <v>6511919</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -949,12 +949,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-04-19</t>
+          <t>2023-05-08</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-04-19</t>
+          <t>2023-05-08</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123158461</v>
+        <v>123158441</v>
       </c>
       <c r="B5" t="n">
-        <v>58346</v>
+        <v>58336</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>208242</v>
+        <v>208250</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mindre vattensalamander</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lissotriton vulgaris</t>
+          <t>Rana arvalis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Nilsson, 1842</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>440479</v>
+        <v>440509</v>
       </c>
       <c r="R5" t="n">
-        <v>6511921</v>
+        <v>6511915</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1051,12 +1051,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-04-17</t>
+          <t>2023-04-19</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-04-17</t>
+          <t>2023-04-19</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123158424</v>
+        <v>123158448</v>
       </c>
       <c r="B6" t="n">
-        <v>58310</v>
+        <v>58336</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>208245</v>
+        <v>208250</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Rana arvalis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Nilsson, 1842</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>440481</v>
+        <v>440528</v>
       </c>
       <c r="R6" t="n">
-        <v>6511927</v>
+        <v>6511918</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1153,12 +1153,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2023-05-08</t>
+          <t>2023-04-19</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2023-05-08</t>
+          <t>2023-04-19</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1185,7 +1185,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123158431</v>
+        <v>123158440</v>
       </c>
       <c r="B7" t="n">
         <v>58336</v>
@@ -1225,7 +1225,7 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>440509</v>
+        <v>440491</v>
       </c>
       <c r="R7" t="n">
         <v>6511891</v>
@@ -1255,12 +1255,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2023-05-08</t>
+          <t>2023-04-19</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2023-05-08</t>
+          <t>2023-04-19</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123158452</v>
+        <v>123158430</v>
       </c>
       <c r="B8" t="n">
-        <v>58336</v>
+        <v>56429</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,21 +1303,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>208250</v>
+        <v>208257</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Kopparödla</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Anguis fragilis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>440487</v>
+        <v>440506</v>
       </c>
       <c r="R8" t="n">
-        <v>6511899</v>
+        <v>6511890</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1357,12 +1357,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2023-04-19</t>
+          <t>2023-05-08</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2023-04-19</t>
+          <t>2023-05-08</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123158460</v>
+        <v>123158426</v>
       </c>
       <c r="B9" t="n">
-        <v>58346</v>
+        <v>58336</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1405,21 +1405,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>208242</v>
+        <v>208250</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mindre vattensalamander</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lissotriton vulgaris</t>
+          <t>Rana arvalis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Nilsson, 1842</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>440478</v>
+        <v>440498</v>
       </c>
       <c r="R9" t="n">
-        <v>6511923</v>
+        <v>6511919</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1459,12 +1459,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2023-04-17</t>
+          <t>2023-05-08</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2023-04-17</t>
+          <t>2023-05-08</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1491,7 +1491,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123158427</v>
+        <v>123158431</v>
       </c>
       <c r="B10" t="n">
         <v>58336</v>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>440503</v>
+        <v>440509</v>
       </c>
       <c r="R10" t="n">
-        <v>6511919</v>
+        <v>6511891</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123158451</v>
+        <v>123158433</v>
       </c>
       <c r="B11" t="n">
-        <v>58336</v>
+        <v>58346</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1609,21 +1609,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>208250</v>
+        <v>208242</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Mindre vattensalamander</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Lissotriton vulgaris</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>440494</v>
+        <v>440506</v>
       </c>
       <c r="R11" t="n">
-        <v>6511873</v>
+        <v>6511891</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1663,12 +1663,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2023-04-20</t>
+          <t>2023-05-08</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2023-04-20</t>
+          <t>2023-05-08</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1695,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123158440</v>
+        <v>123158443</v>
       </c>
       <c r="B12" t="n">
-        <v>58336</v>
+        <v>56437</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1711,21 +1711,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>208250</v>
+        <v>208255</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Skogsödla</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Zootoca vivipara</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
+          <t>(Jacquin, 1787)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1735,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>440491</v>
+        <v>440500</v>
       </c>
       <c r="R12" t="n">
-        <v>6511891</v>
+        <v>6511916</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1797,10 +1797,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123158426</v>
+        <v>123158460</v>
       </c>
       <c r="B13" t="n">
-        <v>58336</v>
+        <v>58346</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1813,21 +1813,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>208250</v>
+        <v>208242</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Mindre vattensalamander</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Lissotriton vulgaris</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>440498</v>
+        <v>440478</v>
       </c>
       <c r="R13" t="n">
-        <v>6511919</v>
+        <v>6511923</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1867,12 +1867,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2023-05-08</t>
+          <t>2023-04-17</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2023-05-08</t>
+          <t>2023-04-17</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1899,10 +1899,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123158443</v>
+        <v>123158461</v>
       </c>
       <c r="B14" t="n">
-        <v>56437</v>
+        <v>58346</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1915,21 +1915,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>208255</v>
+        <v>208242</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skogsödla</t>
+          <t>Mindre vattensalamander</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Zootoca vivipara</t>
+          <t>Lissotriton vulgaris</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Jacquin, 1787)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1939,10 +1939,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>440500</v>
+        <v>440479</v>
       </c>
       <c r="R14" t="n">
-        <v>6511916</v>
+        <v>6511921</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -1969,12 +1969,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2023-04-19</t>
+          <t>2023-04-17</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2023-04-19</t>
+          <t>2023-04-17</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2001,10 +2001,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123158430</v>
+        <v>123158452</v>
       </c>
       <c r="B15" t="n">
-        <v>56429</v>
+        <v>58336</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2017,21 +2017,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>208257</v>
+        <v>208250</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kopparödla</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Anguis fragilis</t>
+          <t>Rana arvalis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Nilsson, 1842</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2041,10 +2041,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>440506</v>
+        <v>440487</v>
       </c>
       <c r="R15" t="n">
-        <v>6511890</v>
+        <v>6511899</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2071,12 +2071,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2023-05-08</t>
+          <t>2023-04-19</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2023-05-08</t>
+          <t>2023-04-19</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2103,10 +2103,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123158441</v>
+        <v>123158424</v>
       </c>
       <c r="B16" t="n">
-        <v>58336</v>
+        <v>58310</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2119,21 +2119,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>208250</v>
+        <v>208245</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2143,10 +2143,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>440509</v>
+        <v>440481</v>
       </c>
       <c r="R16" t="n">
-        <v>6511915</v>
+        <v>6511927</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2173,12 +2173,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2023-04-19</t>
+          <t>2023-05-08</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2023-04-19</t>
+          <t>2023-05-08</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2205,7 +2205,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123158446</v>
+        <v>123158451</v>
       </c>
       <c r="B17" t="n">
         <v>58336</v>
@@ -2245,10 +2245,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>440510</v>
+        <v>440494</v>
       </c>
       <c r="R17" t="n">
-        <v>6511914</v>
+        <v>6511873</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2275,12 +2275,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2023-04-19</t>
+          <t>2023-04-20</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2023-04-19</t>
+          <t>2023-04-20</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2409,10 +2409,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123158433</v>
+        <v>123158446</v>
       </c>
       <c r="B19" t="n">
-        <v>58346</v>
+        <v>58336</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2425,21 +2425,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>208242</v>
+        <v>208250</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mindre vattensalamander</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lissotriton vulgaris</t>
+          <t>Rana arvalis</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Nilsson, 1842</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2449,10 +2449,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>440506</v>
+        <v>440510</v>
       </c>
       <c r="R19" t="n">
-        <v>6511891</v>
+        <v>6511914</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2479,12 +2479,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2023-05-08</t>
+          <t>2023-04-19</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2023-05-08</t>
+          <t>2023-04-19</t>
         </is>
       </c>
       <c r="AD19" t="b">

--- a/artfynd/A 46932-2020 artfynd.xlsx
+++ b/artfynd/A 46932-2020 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123158425</v>
+        <v>123158440</v>
       </c>
       <c r="B2" t="n">
         <v>58336</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>440504</v>
+        <v>440491</v>
       </c>
       <c r="R2" t="n">
-        <v>6511909</v>
+        <v>6511891</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -745,12 +745,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-05-08</t>
+          <t>2023-04-19</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-05-08</t>
+          <t>2023-04-19</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123158428</v>
+        <v>123158427</v>
       </c>
       <c r="B3" t="n">
         <v>58336</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>440508</v>
+        <v>440503</v>
       </c>
       <c r="R3" t="n">
-        <v>6511917</v>
+        <v>6511919</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123158427</v>
+        <v>123158461</v>
       </c>
       <c r="B4" t="n">
-        <v>58336</v>
+        <v>58346</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>208250</v>
+        <v>208242</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Mindre vattensalamander</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Lissotriton vulgaris</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>440503</v>
+        <v>440479</v>
       </c>
       <c r="R4" t="n">
-        <v>6511919</v>
+        <v>6511921</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -949,12 +949,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-05-08</t>
+          <t>2023-04-17</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-05-08</t>
+          <t>2023-04-17</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123158448</v>
+        <v>123158424</v>
       </c>
       <c r="B6" t="n">
-        <v>58336</v>
+        <v>58310</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>208250</v>
+        <v>208245</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>440528</v>
+        <v>440481</v>
       </c>
       <c r="R6" t="n">
-        <v>6511918</v>
+        <v>6511927</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1153,12 +1153,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2023-04-19</t>
+          <t>2023-05-08</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2023-04-19</t>
+          <t>2023-05-08</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1185,7 +1185,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123158440</v>
+        <v>123158451</v>
       </c>
       <c r="B7" t="n">
         <v>58336</v>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>440491</v>
+        <v>440494</v>
       </c>
       <c r="R7" t="n">
-        <v>6511891</v>
+        <v>6511873</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1255,12 +1255,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2023-04-19</t>
+          <t>2023-04-20</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2023-04-19</t>
+          <t>2023-04-20</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123158430</v>
+        <v>123158446</v>
       </c>
       <c r="B8" t="n">
-        <v>56429</v>
+        <v>58336</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,21 +1303,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>208257</v>
+        <v>208250</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kopparödla</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Anguis fragilis</t>
+          <t>Rana arvalis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Nilsson, 1842</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>440506</v>
+        <v>440510</v>
       </c>
       <c r="R8" t="n">
-        <v>6511890</v>
+        <v>6511914</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1357,12 +1357,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2023-05-08</t>
+          <t>2023-04-19</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2023-05-08</t>
+          <t>2023-04-19</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1389,7 +1389,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123158426</v>
+        <v>123158431</v>
       </c>
       <c r="B9" t="n">
         <v>58336</v>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>440498</v>
+        <v>440509</v>
       </c>
       <c r="R9" t="n">
-        <v>6511919</v>
+        <v>6511891</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1491,7 +1491,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123158431</v>
+        <v>123158445</v>
       </c>
       <c r="B10" t="n">
         <v>58336</v>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>440509</v>
+        <v>440506</v>
       </c>
       <c r="R10" t="n">
-        <v>6511891</v>
+        <v>6511913</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1561,12 +1561,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2023-05-08</t>
+          <t>2023-04-19</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2023-05-08</t>
+          <t>2023-04-19</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123158433</v>
+        <v>123158426</v>
       </c>
       <c r="B11" t="n">
-        <v>58346</v>
+        <v>58336</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1609,21 +1609,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>208242</v>
+        <v>208250</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mindre vattensalamander</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lissotriton vulgaris</t>
+          <t>Rana arvalis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Nilsson, 1842</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>440506</v>
+        <v>440498</v>
       </c>
       <c r="R11" t="n">
-        <v>6511891</v>
+        <v>6511919</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1695,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123158443</v>
+        <v>123158428</v>
       </c>
       <c r="B12" t="n">
-        <v>56437</v>
+        <v>58336</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1711,21 +1711,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>208255</v>
+        <v>208250</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skogsödla</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Zootoca vivipara</t>
+          <t>Rana arvalis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Jacquin, 1787)</t>
+          <t>Nilsson, 1842</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1735,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>440500</v>
+        <v>440508</v>
       </c>
       <c r="R12" t="n">
-        <v>6511916</v>
+        <v>6511917</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1765,12 +1765,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2023-04-19</t>
+          <t>2023-05-08</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2023-04-19</t>
+          <t>2023-05-08</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1899,10 +1899,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123158461</v>
+        <v>123158443</v>
       </c>
       <c r="B14" t="n">
-        <v>58346</v>
+        <v>56437</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1915,21 +1915,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>208242</v>
+        <v>208255</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mindre vattensalamander</t>
+          <t>Skogsödla</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lissotriton vulgaris</t>
+          <t>Zootoca vivipara</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Jacquin, 1787)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1939,10 +1939,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>440479</v>
+        <v>440500</v>
       </c>
       <c r="R14" t="n">
-        <v>6511921</v>
+        <v>6511916</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -1969,12 +1969,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2023-04-17</t>
+          <t>2023-04-19</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2023-04-17</t>
+          <t>2023-04-19</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2001,10 +2001,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123158452</v>
+        <v>123158430</v>
       </c>
       <c r="B15" t="n">
-        <v>58336</v>
+        <v>56429</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2017,21 +2017,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>208250</v>
+        <v>208257</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Kopparödla</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Anguis fragilis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2041,10 +2041,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>440487</v>
+        <v>440506</v>
       </c>
       <c r="R15" t="n">
-        <v>6511899</v>
+        <v>6511890</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2071,12 +2071,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2023-04-19</t>
+          <t>2023-05-08</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2023-04-19</t>
+          <t>2023-05-08</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2103,10 +2103,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123158424</v>
+        <v>123158433</v>
       </c>
       <c r="B16" t="n">
-        <v>58310</v>
+        <v>58346</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2119,16 +2119,16 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>208245</v>
+        <v>208242</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Mindre vattensalamander</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Lissotriton vulgaris</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2143,10 +2143,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>440481</v>
+        <v>440506</v>
       </c>
       <c r="R16" t="n">
-        <v>6511927</v>
+        <v>6511891</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2205,7 +2205,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123158451</v>
+        <v>123158452</v>
       </c>
       <c r="B17" t="n">
         <v>58336</v>
@@ -2245,10 +2245,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>440494</v>
+        <v>440487</v>
       </c>
       <c r="R17" t="n">
-        <v>6511873</v>
+        <v>6511899</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2275,12 +2275,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2023-04-20</t>
+          <t>2023-04-19</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2023-04-20</t>
+          <t>2023-04-19</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2307,7 +2307,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123158445</v>
+        <v>123158448</v>
       </c>
       <c r="B18" t="n">
         <v>58336</v>
@@ -2347,10 +2347,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>440506</v>
+        <v>440528</v>
       </c>
       <c r="R18" t="n">
-        <v>6511913</v>
+        <v>6511918</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2409,7 +2409,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123158446</v>
+        <v>123158425</v>
       </c>
       <c r="B19" t="n">
         <v>58336</v>
@@ -2449,10 +2449,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>440510</v>
+        <v>440504</v>
       </c>
       <c r="R19" t="n">
-        <v>6511914</v>
+        <v>6511909</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2479,12 +2479,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2023-04-19</t>
+          <t>2023-05-08</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2023-04-19</t>
+          <t>2023-05-08</t>
         </is>
       </c>
       <c r="AD19" t="b">

--- a/artfynd/A 46932-2020 artfynd.xlsx
+++ b/artfynd/A 46932-2020 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123158427</v>
+        <v>123158461</v>
       </c>
       <c r="B3" t="n">
-        <v>58336</v>
+        <v>58346</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>208250</v>
+        <v>208242</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Mindre vattensalamander</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Lissotriton vulgaris</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>440503</v>
+        <v>440479</v>
       </c>
       <c r="R3" t="n">
-        <v>6511919</v>
+        <v>6511921</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -847,12 +847,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-05-08</t>
+          <t>2023-04-17</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-05-08</t>
+          <t>2023-04-17</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123158461</v>
+        <v>123158441</v>
       </c>
       <c r="B4" t="n">
-        <v>58346</v>
+        <v>58336</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>208242</v>
+        <v>208250</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mindre vattensalamander</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lissotriton vulgaris</t>
+          <t>Rana arvalis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Nilsson, 1842</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>440479</v>
+        <v>440509</v>
       </c>
       <c r="R4" t="n">
-        <v>6511921</v>
+        <v>6511915</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -949,12 +949,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-04-17</t>
+          <t>2023-04-19</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-04-17</t>
+          <t>2023-04-19</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123158441</v>
+        <v>123158443</v>
       </c>
       <c r="B5" t="n">
-        <v>58336</v>
+        <v>56437</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>208250</v>
+        <v>208255</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Skogsödla</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Zootoca vivipara</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
+          <t>(Jacquin, 1787)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>440509</v>
+        <v>440500</v>
       </c>
       <c r="R5" t="n">
-        <v>6511915</v>
+        <v>6511916</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123158424</v>
+        <v>123158448</v>
       </c>
       <c r="B6" t="n">
-        <v>58310</v>
+        <v>58336</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>208245</v>
+        <v>208250</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Rana arvalis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Nilsson, 1842</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>440481</v>
+        <v>440528</v>
       </c>
       <c r="R6" t="n">
-        <v>6511927</v>
+        <v>6511918</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1153,12 +1153,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2023-05-08</t>
+          <t>2023-04-19</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2023-05-08</t>
+          <t>2023-04-19</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1185,7 +1185,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123158451</v>
+        <v>123158445</v>
       </c>
       <c r="B7" t="n">
         <v>58336</v>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>440494</v>
+        <v>440506</v>
       </c>
       <c r="R7" t="n">
-        <v>6511873</v>
+        <v>6511913</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1255,12 +1255,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2023-04-20</t>
+          <t>2023-04-19</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2023-04-20</t>
+          <t>2023-04-19</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123158445</v>
+        <v>123158433</v>
       </c>
       <c r="B10" t="n">
-        <v>58336</v>
+        <v>58346</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1507,21 +1507,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>208250</v>
+        <v>208242</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Mindre vattensalamander</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Lissotriton vulgaris</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1534,7 +1534,7 @@
         <v>440506</v>
       </c>
       <c r="R10" t="n">
-        <v>6511913</v>
+        <v>6511891</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1561,12 +1561,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2023-04-19</t>
+          <t>2023-05-08</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2023-04-19</t>
+          <t>2023-05-08</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1593,7 +1593,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123158426</v>
+        <v>123158427</v>
       </c>
       <c r="B11" t="n">
         <v>58336</v>
@@ -1633,7 +1633,7 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>440498</v>
+        <v>440503</v>
       </c>
       <c r="R11" t="n">
         <v>6511919</v>
@@ -1695,7 +1695,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123158428</v>
+        <v>123158425</v>
       </c>
       <c r="B12" t="n">
         <v>58336</v>
@@ -1735,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>440508</v>
+        <v>440504</v>
       </c>
       <c r="R12" t="n">
-        <v>6511917</v>
+        <v>6511909</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1797,10 +1797,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123158460</v>
+        <v>123158426</v>
       </c>
       <c r="B13" t="n">
-        <v>58346</v>
+        <v>58336</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1813,21 +1813,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>208242</v>
+        <v>208250</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mindre vattensalamander</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lissotriton vulgaris</t>
+          <t>Rana arvalis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Nilsson, 1842</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>440478</v>
+        <v>440498</v>
       </c>
       <c r="R13" t="n">
-        <v>6511923</v>
+        <v>6511919</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1867,12 +1867,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2023-04-17</t>
+          <t>2023-05-08</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2023-04-17</t>
+          <t>2023-05-08</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1899,10 +1899,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123158443</v>
+        <v>123158428</v>
       </c>
       <c r="B14" t="n">
-        <v>56437</v>
+        <v>58336</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1915,21 +1915,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>208255</v>
+        <v>208250</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skogsödla</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Zootoca vivipara</t>
+          <t>Rana arvalis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Jacquin, 1787)</t>
+          <t>Nilsson, 1842</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1939,10 +1939,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>440500</v>
+        <v>440508</v>
       </c>
       <c r="R14" t="n">
-        <v>6511916</v>
+        <v>6511917</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -1969,12 +1969,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2023-04-19</t>
+          <t>2023-05-08</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2023-04-19</t>
+          <t>2023-05-08</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2103,10 +2103,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123158433</v>
+        <v>123158424</v>
       </c>
       <c r="B16" t="n">
-        <v>58346</v>
+        <v>58310</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2119,16 +2119,16 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>208242</v>
+        <v>208245</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mindre vattensalamander</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lissotriton vulgaris</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2143,10 +2143,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>440506</v>
+        <v>440481</v>
       </c>
       <c r="R16" t="n">
-        <v>6511891</v>
+        <v>6511927</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2205,7 +2205,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123158452</v>
+        <v>123158451</v>
       </c>
       <c r="B17" t="n">
         <v>58336</v>
@@ -2245,10 +2245,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>440487</v>
+        <v>440494</v>
       </c>
       <c r="R17" t="n">
-        <v>6511899</v>
+        <v>6511873</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2275,12 +2275,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2023-04-19</t>
+          <t>2023-04-20</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2023-04-19</t>
+          <t>2023-04-20</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2307,7 +2307,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123158448</v>
+        <v>123158452</v>
       </c>
       <c r="B18" t="n">
         <v>58336</v>
@@ -2347,10 +2347,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>440528</v>
+        <v>440487</v>
       </c>
       <c r="R18" t="n">
-        <v>6511918</v>
+        <v>6511899</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2409,10 +2409,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123158425</v>
+        <v>123158460</v>
       </c>
       <c r="B19" t="n">
-        <v>58336</v>
+        <v>58346</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2425,21 +2425,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>208250</v>
+        <v>208242</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Mindre vattensalamander</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Lissotriton vulgaris</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2449,10 +2449,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>440504</v>
+        <v>440478</v>
       </c>
       <c r="R19" t="n">
-        <v>6511909</v>
+        <v>6511923</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2479,12 +2479,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2023-05-08</t>
+          <t>2023-04-17</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2023-05-08</t>
+          <t>2023-04-17</t>
         </is>
       </c>
       <c r="AD19" t="b">

--- a/artfynd/A 46932-2020 artfynd.xlsx
+++ b/artfynd/A 46932-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123158440</v>
+        <v>123158428</v>
       </c>
       <c r="B2" t="n">
-        <v>58336</v>
+        <v>58339</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>440491</v>
+        <v>440508</v>
       </c>
       <c r="R2" t="n">
-        <v>6511891</v>
+        <v>6511917</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -745,12 +745,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-04-19</t>
+          <t>2023-05-08</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-04-19</t>
+          <t>2023-05-08</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123158461</v>
+        <v>123158424</v>
       </c>
       <c r="B3" t="n">
-        <v>58346</v>
+        <v>58313</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,16 +793,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>208242</v>
+        <v>208245</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mindre vattensalamander</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lissotriton vulgaris</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>440479</v>
+        <v>440481</v>
       </c>
       <c r="R3" t="n">
-        <v>6511921</v>
+        <v>6511927</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -847,12 +847,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-04-17</t>
+          <t>2023-05-08</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-04-17</t>
+          <t>2023-05-08</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123158441</v>
+        <v>123158431</v>
       </c>
       <c r="B4" t="n">
-        <v>58336</v>
+        <v>58339</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -922,7 +922,7 @@
         <v>440509</v>
       </c>
       <c r="R4" t="n">
-        <v>6511915</v>
+        <v>6511891</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -949,12 +949,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-04-19</t>
+          <t>2023-05-08</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-04-19</t>
+          <t>2023-05-08</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123158443</v>
+        <v>123158426</v>
       </c>
       <c r="B5" t="n">
-        <v>56437</v>
+        <v>58339</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>208255</v>
+        <v>208250</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skogsödla</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Zootoca vivipara</t>
+          <t>Rana arvalis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Jacquin, 1787)</t>
+          <t>Nilsson, 1842</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>440500</v>
+        <v>440498</v>
       </c>
       <c r="R5" t="n">
-        <v>6511916</v>
+        <v>6511919</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1051,12 +1051,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-04-19</t>
+          <t>2023-05-08</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-04-19</t>
+          <t>2023-05-08</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123158448</v>
+        <v>123158445</v>
       </c>
       <c r="B6" t="n">
-        <v>58336</v>
+        <v>58339</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>440528</v>
+        <v>440506</v>
       </c>
       <c r="R6" t="n">
-        <v>6511918</v>
+        <v>6511913</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123158445</v>
+        <v>123158460</v>
       </c>
       <c r="B7" t="n">
-        <v>58336</v>
+        <v>58349</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>208250</v>
+        <v>208242</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Mindre vattensalamander</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Lissotriton vulgaris</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>440506</v>
+        <v>440478</v>
       </c>
       <c r="R7" t="n">
-        <v>6511913</v>
+        <v>6511923</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1255,12 +1255,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2023-04-19</t>
+          <t>2023-04-17</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2023-04-19</t>
+          <t>2023-04-17</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123158446</v>
+        <v>123158461</v>
       </c>
       <c r="B8" t="n">
-        <v>58336</v>
+        <v>58349</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,21 +1303,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>208250</v>
+        <v>208242</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Mindre vattensalamander</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Lissotriton vulgaris</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>440510</v>
+        <v>440479</v>
       </c>
       <c r="R8" t="n">
-        <v>6511914</v>
+        <v>6511921</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1357,12 +1357,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2023-04-19</t>
+          <t>2023-04-17</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2023-04-19</t>
+          <t>2023-04-17</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123158431</v>
+        <v>123158441</v>
       </c>
       <c r="B9" t="n">
-        <v>58336</v>
+        <v>58339</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1432,7 +1432,7 @@
         <v>440509</v>
       </c>
       <c r="R9" t="n">
-        <v>6511891</v>
+        <v>6511915</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1459,12 +1459,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2023-05-08</t>
+          <t>2023-04-19</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2023-05-08</t>
+          <t>2023-04-19</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123158433</v>
+        <v>123158427</v>
       </c>
       <c r="B10" t="n">
-        <v>58346</v>
+        <v>58339</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1507,21 +1507,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>208242</v>
+        <v>208250</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mindre vattensalamander</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lissotriton vulgaris</t>
+          <t>Rana arvalis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Nilsson, 1842</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>440506</v>
+        <v>440503</v>
       </c>
       <c r="R10" t="n">
-        <v>6511891</v>
+        <v>6511919</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123158427</v>
+        <v>123158425</v>
       </c>
       <c r="B11" t="n">
-        <v>58336</v>
+        <v>58339</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>440503</v>
+        <v>440504</v>
       </c>
       <c r="R11" t="n">
-        <v>6511919</v>
+        <v>6511909</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1695,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123158425</v>
+        <v>123158440</v>
       </c>
       <c r="B12" t="n">
-        <v>58336</v>
+        <v>58339</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1735,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>440504</v>
+        <v>440491</v>
       </c>
       <c r="R12" t="n">
-        <v>6511909</v>
+        <v>6511891</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1765,12 +1765,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2023-05-08</t>
+          <t>2023-04-19</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2023-05-08</t>
+          <t>2023-04-19</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1797,10 +1797,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123158426</v>
+        <v>123158443</v>
       </c>
       <c r="B13" t="n">
-        <v>58336</v>
+        <v>56440</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1813,21 +1813,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>208250</v>
+        <v>208255</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Skogsödla</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Zootoca vivipara</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
+          <t>(Jacquin, 1787)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>440498</v>
+        <v>440500</v>
       </c>
       <c r="R13" t="n">
-        <v>6511919</v>
+        <v>6511916</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1867,12 +1867,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2023-05-08</t>
+          <t>2023-04-19</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2023-05-08</t>
+          <t>2023-04-19</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1899,10 +1899,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123158428</v>
+        <v>123158446</v>
       </c>
       <c r="B14" t="n">
-        <v>58336</v>
+        <v>58339</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1939,10 +1939,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>440508</v>
+        <v>440510</v>
       </c>
       <c r="R14" t="n">
-        <v>6511917</v>
+        <v>6511914</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -1969,12 +1969,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2023-05-08</t>
+          <t>2023-04-19</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2023-05-08</t>
+          <t>2023-04-19</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2001,10 +2001,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123158430</v>
+        <v>123158452</v>
       </c>
       <c r="B15" t="n">
-        <v>56429</v>
+        <v>58339</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2017,21 +2017,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>208257</v>
+        <v>208250</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kopparödla</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Anguis fragilis</t>
+          <t>Rana arvalis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Nilsson, 1842</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2041,10 +2041,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>440506</v>
+        <v>440487</v>
       </c>
       <c r="R15" t="n">
-        <v>6511890</v>
+        <v>6511899</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2071,12 +2071,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2023-05-08</t>
+          <t>2023-04-19</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2023-05-08</t>
+          <t>2023-04-19</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2103,10 +2103,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123158424</v>
+        <v>123158430</v>
       </c>
       <c r="B16" t="n">
-        <v>58310</v>
+        <v>56432</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2119,21 +2119,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>208245</v>
+        <v>208257</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Kopparödla</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Anguis fragilis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2143,10 +2143,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>440481</v>
+        <v>440506</v>
       </c>
       <c r="R16" t="n">
-        <v>6511927</v>
+        <v>6511890</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2205,10 +2205,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123158451</v>
+        <v>123158448</v>
       </c>
       <c r="B17" t="n">
-        <v>58336</v>
+        <v>58339</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2245,10 +2245,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>440494</v>
+        <v>440528</v>
       </c>
       <c r="R17" t="n">
-        <v>6511873</v>
+        <v>6511918</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2275,12 +2275,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2023-04-20</t>
+          <t>2023-04-19</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2023-04-20</t>
+          <t>2023-04-19</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2307,10 +2307,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123158452</v>
+        <v>123158451</v>
       </c>
       <c r="B18" t="n">
-        <v>58336</v>
+        <v>58339</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2347,10 +2347,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>440487</v>
+        <v>440494</v>
       </c>
       <c r="R18" t="n">
-        <v>6511899</v>
+        <v>6511873</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2377,12 +2377,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2023-04-19</t>
+          <t>2023-04-20</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2023-04-19</t>
+          <t>2023-04-20</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2409,10 +2409,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123158460</v>
+        <v>123158433</v>
       </c>
       <c r="B19" t="n">
-        <v>58346</v>
+        <v>58349</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2449,10 +2449,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>440478</v>
+        <v>440506</v>
       </c>
       <c r="R19" t="n">
-        <v>6511923</v>
+        <v>6511891</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2479,12 +2479,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2023-04-17</t>
+          <t>2023-05-08</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2023-04-17</t>
+          <t>2023-05-08</t>
         </is>
       </c>
       <c r="AD19" t="b">

--- a/artfynd/A 46932-2020 artfynd.xlsx
+++ b/artfynd/A 46932-2020 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123158424</v>
+        <v>123158446</v>
       </c>
       <c r="B3" t="n">
-        <v>58313</v>
+        <v>58339</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>208245</v>
+        <v>208250</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Rana arvalis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Nilsson, 1842</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>440481</v>
+        <v>440510</v>
       </c>
       <c r="R3" t="n">
-        <v>6511927</v>
+        <v>6511914</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -847,12 +847,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-05-08</t>
+          <t>2023-04-19</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-05-08</t>
+          <t>2023-04-19</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -981,7 +981,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123158426</v>
+        <v>123158427</v>
       </c>
       <c r="B5" t="n">
         <v>58339</v>
@@ -1021,7 +1021,7 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>440498</v>
+        <v>440503</v>
       </c>
       <c r="R5" t="n">
         <v>6511919</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123158445</v>
+        <v>123158460</v>
       </c>
       <c r="B6" t="n">
-        <v>58339</v>
+        <v>58349</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>208250</v>
+        <v>208242</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Mindre vattensalamander</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Lissotriton vulgaris</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>440506</v>
+        <v>440478</v>
       </c>
       <c r="R6" t="n">
-        <v>6511913</v>
+        <v>6511923</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1153,12 +1153,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2023-04-19</t>
+          <t>2023-04-17</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2023-04-19</t>
+          <t>2023-04-17</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123158460</v>
+        <v>123158448</v>
       </c>
       <c r="B7" t="n">
-        <v>58349</v>
+        <v>58339</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>208242</v>
+        <v>208250</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mindre vattensalamander</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lissotriton vulgaris</t>
+          <t>Rana arvalis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Nilsson, 1842</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>440478</v>
+        <v>440528</v>
       </c>
       <c r="R7" t="n">
-        <v>6511923</v>
+        <v>6511918</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1255,12 +1255,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2023-04-17</t>
+          <t>2023-04-19</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2023-04-17</t>
+          <t>2023-04-19</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123158461</v>
+        <v>123158426</v>
       </c>
       <c r="B8" t="n">
-        <v>58349</v>
+        <v>58339</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,21 +1303,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>208242</v>
+        <v>208250</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mindre vattensalamander</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lissotriton vulgaris</t>
+          <t>Rana arvalis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Nilsson, 1842</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>440479</v>
+        <v>440498</v>
       </c>
       <c r="R8" t="n">
-        <v>6511921</v>
+        <v>6511919</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1357,12 +1357,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2023-04-17</t>
+          <t>2023-05-08</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2023-04-17</t>
+          <t>2023-05-08</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1491,7 +1491,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123158427</v>
+        <v>123158452</v>
       </c>
       <c r="B10" t="n">
         <v>58339</v>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>440503</v>
+        <v>440487</v>
       </c>
       <c r="R10" t="n">
-        <v>6511919</v>
+        <v>6511899</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1561,12 +1561,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2023-05-08</t>
+          <t>2023-04-19</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2023-05-08</t>
+          <t>2023-04-19</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123158425</v>
+        <v>123158424</v>
       </c>
       <c r="B11" t="n">
-        <v>58339</v>
+        <v>58313</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1609,21 +1609,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>208250</v>
+        <v>208245</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>440504</v>
+        <v>440481</v>
       </c>
       <c r="R11" t="n">
-        <v>6511909</v>
+        <v>6511927</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1695,7 +1695,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123158440</v>
+        <v>123158451</v>
       </c>
       <c r="B12" t="n">
         <v>58339</v>
@@ -1735,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>440491</v>
+        <v>440494</v>
       </c>
       <c r="R12" t="n">
-        <v>6511891</v>
+        <v>6511873</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1765,12 +1765,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2023-04-19</t>
+          <t>2023-04-20</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2023-04-19</t>
+          <t>2023-04-20</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1797,10 +1797,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123158443</v>
+        <v>123158440</v>
       </c>
       <c r="B13" t="n">
-        <v>56440</v>
+        <v>58339</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1813,21 +1813,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>208255</v>
+        <v>208250</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skogsödla</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Zootoca vivipara</t>
+          <t>Rana arvalis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Jacquin, 1787)</t>
+          <t>Nilsson, 1842</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>440500</v>
+        <v>440491</v>
       </c>
       <c r="R13" t="n">
-        <v>6511916</v>
+        <v>6511891</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1899,7 +1899,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123158446</v>
+        <v>123158425</v>
       </c>
       <c r="B14" t="n">
         <v>58339</v>
@@ -1939,10 +1939,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>440510</v>
+        <v>440504</v>
       </c>
       <c r="R14" t="n">
-        <v>6511914</v>
+        <v>6511909</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -1969,12 +1969,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2023-04-19</t>
+          <t>2023-05-08</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2023-04-19</t>
+          <t>2023-05-08</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2001,10 +2001,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123158452</v>
+        <v>123158433</v>
       </c>
       <c r="B15" t="n">
-        <v>58339</v>
+        <v>58349</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2017,21 +2017,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>208250</v>
+        <v>208242</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Mindre vattensalamander</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Lissotriton vulgaris</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2041,10 +2041,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>440487</v>
+        <v>440506</v>
       </c>
       <c r="R15" t="n">
-        <v>6511899</v>
+        <v>6511891</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2071,12 +2071,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2023-04-19</t>
+          <t>2023-05-08</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2023-04-19</t>
+          <t>2023-05-08</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2103,10 +2103,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123158430</v>
+        <v>123158461</v>
       </c>
       <c r="B16" t="n">
-        <v>56432</v>
+        <v>58349</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2119,21 +2119,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>208257</v>
+        <v>208242</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kopparödla</t>
+          <t>Mindre vattensalamander</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Anguis fragilis</t>
+          <t>Lissotriton vulgaris</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2143,10 +2143,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>440506</v>
+        <v>440479</v>
       </c>
       <c r="R16" t="n">
-        <v>6511890</v>
+        <v>6511921</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2173,12 +2173,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2023-05-08</t>
+          <t>2023-04-17</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2023-05-08</t>
+          <t>2023-04-17</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2205,7 +2205,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123158448</v>
+        <v>123158445</v>
       </c>
       <c r="B17" t="n">
         <v>58339</v>
@@ -2245,10 +2245,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>440528</v>
+        <v>440506</v>
       </c>
       <c r="R17" t="n">
-        <v>6511918</v>
+        <v>6511913</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2307,10 +2307,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123158451</v>
+        <v>123158443</v>
       </c>
       <c r="B18" t="n">
-        <v>58339</v>
+        <v>56440</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2323,21 +2323,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>208250</v>
+        <v>208255</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Skogsödla</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Zootoca vivipara</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
+          <t>(Jacquin, 1787)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2347,10 +2347,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>440494</v>
+        <v>440500</v>
       </c>
       <c r="R18" t="n">
-        <v>6511873</v>
+        <v>6511916</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2377,12 +2377,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2023-04-20</t>
+          <t>2023-04-19</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2023-04-20</t>
+          <t>2023-04-19</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2409,10 +2409,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123158433</v>
+        <v>123158430</v>
       </c>
       <c r="B19" t="n">
-        <v>58349</v>
+        <v>56432</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2425,21 +2425,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>208242</v>
+        <v>208257</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mindre vattensalamander</t>
+          <t>Kopparödla</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lissotriton vulgaris</t>
+          <t>Anguis fragilis</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2452,7 +2452,7 @@
         <v>440506</v>
       </c>
       <c r="R19" t="n">
-        <v>6511891</v>
+        <v>6511890</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>

--- a/artfynd/A 46932-2020 artfynd.xlsx
+++ b/artfynd/A 46932-2020 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123158428</v>
+        <v>123158441</v>
       </c>
       <c r="B2" t="n">
         <v>58339</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>440508</v>
+        <v>440509</v>
       </c>
       <c r="R2" t="n">
-        <v>6511917</v>
+        <v>6511915</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -745,12 +745,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-05-08</t>
+          <t>2023-04-19</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-05-08</t>
+          <t>2023-04-19</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123158446</v>
+        <v>123158460</v>
       </c>
       <c r="B3" t="n">
-        <v>58339</v>
+        <v>58349</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>208250</v>
+        <v>208242</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Mindre vattensalamander</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Lissotriton vulgaris</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>440510</v>
+        <v>440478</v>
       </c>
       <c r="R3" t="n">
-        <v>6511914</v>
+        <v>6511923</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -847,12 +847,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-04-19</t>
+          <t>2023-04-17</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-04-19</t>
+          <t>2023-04-17</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123158431</v>
+        <v>123158424</v>
       </c>
       <c r="B4" t="n">
-        <v>58339</v>
+        <v>58313</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>208250</v>
+        <v>208245</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>440509</v>
+        <v>440481</v>
       </c>
       <c r="R4" t="n">
-        <v>6511891</v>
+        <v>6511927</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -981,7 +981,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123158427</v>
+        <v>123158425</v>
       </c>
       <c r="B5" t="n">
         <v>58339</v>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>440503</v>
+        <v>440504</v>
       </c>
       <c r="R5" t="n">
-        <v>6511919</v>
+        <v>6511909</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123158460</v>
+        <v>123158446</v>
       </c>
       <c r="B6" t="n">
-        <v>58349</v>
+        <v>58339</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>208242</v>
+        <v>208250</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mindre vattensalamander</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lissotriton vulgaris</t>
+          <t>Rana arvalis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Nilsson, 1842</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>440478</v>
+        <v>440510</v>
       </c>
       <c r="R6" t="n">
-        <v>6511923</v>
+        <v>6511914</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1153,12 +1153,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2023-04-17</t>
+          <t>2023-04-19</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2023-04-17</t>
+          <t>2023-04-19</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1185,7 +1185,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123158448</v>
+        <v>123158426</v>
       </c>
       <c r="B7" t="n">
         <v>58339</v>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>440528</v>
+        <v>440498</v>
       </c>
       <c r="R7" t="n">
-        <v>6511918</v>
+        <v>6511919</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1255,12 +1255,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2023-04-19</t>
+          <t>2023-05-08</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2023-04-19</t>
+          <t>2023-05-08</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1287,7 +1287,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123158426</v>
+        <v>123158428</v>
       </c>
       <c r="B8" t="n">
         <v>58339</v>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>440498</v>
+        <v>440508</v>
       </c>
       <c r="R8" t="n">
-        <v>6511919</v>
+        <v>6511917</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1389,7 +1389,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123158441</v>
+        <v>123158440</v>
       </c>
       <c r="B9" t="n">
         <v>58339</v>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>440509</v>
+        <v>440491</v>
       </c>
       <c r="R9" t="n">
-        <v>6511915</v>
+        <v>6511891</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1491,7 +1491,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123158452</v>
+        <v>123158448</v>
       </c>
       <c r="B10" t="n">
         <v>58339</v>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>440487</v>
+        <v>440528</v>
       </c>
       <c r="R10" t="n">
-        <v>6511899</v>
+        <v>6511918</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123158424</v>
+        <v>123158461</v>
       </c>
       <c r="B11" t="n">
-        <v>58313</v>
+        <v>58349</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1609,16 +1609,16 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>208245</v>
+        <v>208242</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Mindre vattensalamander</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Lissotriton vulgaris</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>440481</v>
+        <v>440479</v>
       </c>
       <c r="R11" t="n">
-        <v>6511927</v>
+        <v>6511921</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1663,12 +1663,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2023-05-08</t>
+          <t>2023-04-17</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2023-05-08</t>
+          <t>2023-04-17</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1797,7 +1797,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123158440</v>
+        <v>123158445</v>
       </c>
       <c r="B13" t="n">
         <v>58339</v>
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>440491</v>
+        <v>440506</v>
       </c>
       <c r="R13" t="n">
-        <v>6511891</v>
+        <v>6511913</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1899,7 +1899,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123158425</v>
+        <v>123158427</v>
       </c>
       <c r="B14" t="n">
         <v>58339</v>
@@ -1939,10 +1939,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>440504</v>
+        <v>440503</v>
       </c>
       <c r="R14" t="n">
-        <v>6511909</v>
+        <v>6511919</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2001,10 +2001,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123158433</v>
+        <v>123158431</v>
       </c>
       <c r="B15" t="n">
-        <v>58349</v>
+        <v>58339</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2017,21 +2017,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>208242</v>
+        <v>208250</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mindre vattensalamander</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lissotriton vulgaris</t>
+          <t>Rana arvalis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Nilsson, 1842</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2041,7 +2041,7 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>440506</v>
+        <v>440509</v>
       </c>
       <c r="R15" t="n">
         <v>6511891</v>
@@ -2103,10 +2103,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123158461</v>
+        <v>123158443</v>
       </c>
       <c r="B16" t="n">
-        <v>58349</v>
+        <v>56440</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2119,21 +2119,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>208242</v>
+        <v>208255</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mindre vattensalamander</t>
+          <t>Skogsödla</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lissotriton vulgaris</t>
+          <t>Zootoca vivipara</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Jacquin, 1787)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2143,10 +2143,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>440479</v>
+        <v>440500</v>
       </c>
       <c r="R16" t="n">
-        <v>6511921</v>
+        <v>6511916</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2173,12 +2173,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2023-04-17</t>
+          <t>2023-04-19</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2023-04-17</t>
+          <t>2023-04-19</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2205,10 +2205,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123158445</v>
+        <v>123158430</v>
       </c>
       <c r="B17" t="n">
-        <v>58339</v>
+        <v>56432</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2221,21 +2221,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>208250</v>
+        <v>208257</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Kopparödla</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Anguis fragilis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2248,7 +2248,7 @@
         <v>440506</v>
       </c>
       <c r="R17" t="n">
-        <v>6511913</v>
+        <v>6511890</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2275,12 +2275,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2023-04-19</t>
+          <t>2023-05-08</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2023-04-19</t>
+          <t>2023-05-08</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2307,10 +2307,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123158443</v>
+        <v>123158452</v>
       </c>
       <c r="B18" t="n">
-        <v>56440</v>
+        <v>58339</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2323,21 +2323,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>208255</v>
+        <v>208250</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skogsödla</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Zootoca vivipara</t>
+          <t>Rana arvalis</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Jacquin, 1787)</t>
+          <t>Nilsson, 1842</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2347,10 +2347,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>440500</v>
+        <v>440487</v>
       </c>
       <c r="R18" t="n">
-        <v>6511916</v>
+        <v>6511899</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2409,10 +2409,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123158430</v>
+        <v>123158433</v>
       </c>
       <c r="B19" t="n">
-        <v>56432</v>
+        <v>58349</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2425,21 +2425,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>208257</v>
+        <v>208242</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kopparödla</t>
+          <t>Mindre vattensalamander</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Anguis fragilis</t>
+          <t>Lissotriton vulgaris</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2452,7 +2452,7 @@
         <v>440506</v>
       </c>
       <c r="R19" t="n">
-        <v>6511890</v>
+        <v>6511891</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>

--- a/artfynd/A 46932-2020 artfynd.xlsx
+++ b/artfynd/A 46932-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123158428</v>
+        <v>123158424</v>
       </c>
       <c r="B2" t="n">
-        <v>58339</v>
+        <v>58319</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>208250</v>
+        <v>208245</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>440508</v>
+        <v>440481</v>
       </c>
       <c r="R2" t="n">
-        <v>6511917</v>
+        <v>6511927</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123158461</v>
+        <v>123158460</v>
       </c>
       <c r="B3" t="n">
-        <v>58349</v>
+        <v>58355</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>440479</v>
+        <v>440478</v>
       </c>
       <c r="R3" t="n">
-        <v>6511921</v>
+        <v>6511923</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123158451</v>
+        <v>123158441</v>
       </c>
       <c r="B4" t="n">
-        <v>58339</v>
+        <v>58345</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>440494</v>
+        <v>440509</v>
       </c>
       <c r="R4" t="n">
-        <v>6511873</v>
+        <v>6511915</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -949,12 +949,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-04-20</t>
+          <t>2023-04-19</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-04-20</t>
+          <t>2023-04-19</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123158431</v>
+        <v>123158430</v>
       </c>
       <c r="B5" t="n">
-        <v>58339</v>
+        <v>56438</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>208250</v>
+        <v>208257</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Kopparödla</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Anguis fragilis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>440509</v>
+        <v>440506</v>
       </c>
       <c r="R5" t="n">
-        <v>6511891</v>
+        <v>6511890</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123158430</v>
+        <v>123158428</v>
       </c>
       <c r="B6" t="n">
-        <v>56432</v>
+        <v>58345</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>208257</v>
+        <v>208250</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kopparödla</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Anguis fragilis</t>
+          <t>Rana arvalis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Nilsson, 1842</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>440506</v>
+        <v>440508</v>
       </c>
       <c r="R6" t="n">
-        <v>6511890</v>
+        <v>6511917</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123158440</v>
+        <v>123158461</v>
       </c>
       <c r="B7" t="n">
-        <v>58339</v>
+        <v>58355</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>208250</v>
+        <v>208242</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Mindre vattensalamander</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Lissotriton vulgaris</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>440491</v>
+        <v>440479</v>
       </c>
       <c r="R7" t="n">
-        <v>6511891</v>
+        <v>6511921</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1255,12 +1255,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2023-04-19</t>
+          <t>2023-04-17</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2023-04-19</t>
+          <t>2023-04-17</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123158445</v>
+        <v>123158448</v>
       </c>
       <c r="B8" t="n">
-        <v>58339</v>
+        <v>58345</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>440506</v>
+        <v>440528</v>
       </c>
       <c r="R8" t="n">
-        <v>6511913</v>
+        <v>6511918</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123158441</v>
+        <v>123158426</v>
       </c>
       <c r="B9" t="n">
-        <v>58339</v>
+        <v>58345</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>440509</v>
+        <v>440498</v>
       </c>
       <c r="R9" t="n">
-        <v>6511915</v>
+        <v>6511919</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1459,12 +1459,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2023-04-19</t>
+          <t>2023-05-08</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2023-04-19</t>
+          <t>2023-05-08</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123158424</v>
+        <v>123158445</v>
       </c>
       <c r="B10" t="n">
-        <v>58313</v>
+        <v>58345</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1507,21 +1507,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>208245</v>
+        <v>208250</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Rana arvalis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Nilsson, 1842</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>440481</v>
+        <v>440506</v>
       </c>
       <c r="R10" t="n">
-        <v>6511927</v>
+        <v>6511913</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1561,12 +1561,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2023-05-08</t>
+          <t>2023-04-19</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2023-05-08</t>
+          <t>2023-04-19</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123158460</v>
+        <v>123158427</v>
       </c>
       <c r="B11" t="n">
-        <v>58349</v>
+        <v>58345</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1609,21 +1609,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>208242</v>
+        <v>208250</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mindre vattensalamander</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lissotriton vulgaris</t>
+          <t>Rana arvalis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Nilsson, 1842</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>440478</v>
+        <v>440503</v>
       </c>
       <c r="R11" t="n">
-        <v>6511923</v>
+        <v>6511919</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1663,12 +1663,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2023-04-17</t>
+          <t>2023-05-08</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2023-04-17</t>
+          <t>2023-05-08</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1695,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123158446</v>
+        <v>123158433</v>
       </c>
       <c r="B12" t="n">
-        <v>58339</v>
+        <v>58355</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1711,21 +1711,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>208250</v>
+        <v>208242</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Mindre vattensalamander</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Lissotriton vulgaris</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1735,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>440510</v>
+        <v>440506</v>
       </c>
       <c r="R12" t="n">
-        <v>6511914</v>
+        <v>6511891</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1765,12 +1765,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2023-04-19</t>
+          <t>2023-05-08</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2023-04-19</t>
+          <t>2023-05-08</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1797,10 +1797,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123158443</v>
+        <v>123158440</v>
       </c>
       <c r="B13" t="n">
-        <v>56440</v>
+        <v>58345</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1813,21 +1813,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>208255</v>
+        <v>208250</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skogsödla</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Zootoca vivipara</t>
+          <t>Rana arvalis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Jacquin, 1787)</t>
+          <t>Nilsson, 1842</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>440500</v>
+        <v>440491</v>
       </c>
       <c r="R13" t="n">
-        <v>6511916</v>
+        <v>6511891</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1899,10 +1899,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123158426</v>
+        <v>123158446</v>
       </c>
       <c r="B14" t="n">
-        <v>58339</v>
+        <v>58345</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1939,10 +1939,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>440498</v>
+        <v>440510</v>
       </c>
       <c r="R14" t="n">
-        <v>6511919</v>
+        <v>6511914</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -1969,12 +1969,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2023-05-08</t>
+          <t>2023-04-19</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2023-05-08</t>
+          <t>2023-04-19</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2001,10 +2001,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123158448</v>
+        <v>123158431</v>
       </c>
       <c r="B15" t="n">
-        <v>58339</v>
+        <v>58345</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2041,10 +2041,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>440528</v>
+        <v>440509</v>
       </c>
       <c r="R15" t="n">
-        <v>6511918</v>
+        <v>6511891</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2071,12 +2071,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2023-04-19</t>
+          <t>2023-05-08</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2023-04-19</t>
+          <t>2023-05-08</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2103,10 +2103,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123158427</v>
+        <v>123158452</v>
       </c>
       <c r="B16" t="n">
-        <v>58339</v>
+        <v>58345</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2143,10 +2143,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>440503</v>
+        <v>440487</v>
       </c>
       <c r="R16" t="n">
-        <v>6511919</v>
+        <v>6511899</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2173,12 +2173,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2023-05-08</t>
+          <t>2023-04-19</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2023-05-08</t>
+          <t>2023-04-19</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2205,10 +2205,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123158425</v>
+        <v>123158443</v>
       </c>
       <c r="B17" t="n">
-        <v>58339</v>
+        <v>56446</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2221,21 +2221,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>208250</v>
+        <v>208255</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Skogsödla</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Zootoca vivipara</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
+          <t>(Jacquin, 1787)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2245,10 +2245,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>440504</v>
+        <v>440500</v>
       </c>
       <c r="R17" t="n">
-        <v>6511909</v>
+        <v>6511916</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2275,12 +2275,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2023-05-08</t>
+          <t>2023-04-19</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2023-05-08</t>
+          <t>2023-04-19</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2307,10 +2307,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123158433</v>
+        <v>123158451</v>
       </c>
       <c r="B18" t="n">
-        <v>58349</v>
+        <v>58345</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2323,21 +2323,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>208242</v>
+        <v>208250</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mindre vattensalamander</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lissotriton vulgaris</t>
+          <t>Rana arvalis</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Nilsson, 1842</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2347,10 +2347,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>440506</v>
+        <v>440494</v>
       </c>
       <c r="R18" t="n">
-        <v>6511891</v>
+        <v>6511873</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2377,12 +2377,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2023-05-08</t>
+          <t>2023-04-20</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2023-05-08</t>
+          <t>2023-04-20</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2409,10 +2409,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123158452</v>
+        <v>123158425</v>
       </c>
       <c r="B19" t="n">
-        <v>58339</v>
+        <v>58345</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2449,10 +2449,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>440487</v>
+        <v>440504</v>
       </c>
       <c r="R19" t="n">
-        <v>6511899</v>
+        <v>6511909</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2479,12 +2479,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2023-04-19</t>
+          <t>2023-05-08</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2023-04-19</t>
+          <t>2023-05-08</t>
         </is>
       </c>
       <c r="AD19" t="b">

--- a/artfynd/A 46932-2020 artfynd.xlsx
+++ b/artfynd/A 46932-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123158424</v>
+        <v>123158426</v>
       </c>
       <c r="B2" t="n">
-        <v>58319</v>
+        <v>58348</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>208245</v>
+        <v>208250</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Rana arvalis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Nilsson, 1842</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>440481</v>
+        <v>440498</v>
       </c>
       <c r="R2" t="n">
-        <v>6511927</v>
+        <v>6511919</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123158460</v>
+        <v>123158428</v>
       </c>
       <c r="B3" t="n">
-        <v>58355</v>
+        <v>58348</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>208242</v>
+        <v>208250</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mindre vattensalamander</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lissotriton vulgaris</t>
+          <t>Rana arvalis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Nilsson, 1842</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>440478</v>
+        <v>440508</v>
       </c>
       <c r="R3" t="n">
-        <v>6511923</v>
+        <v>6511917</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -847,12 +847,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-04-17</t>
+          <t>2023-05-08</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-04-17</t>
+          <t>2023-05-08</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123158441</v>
+        <v>123158451</v>
       </c>
       <c r="B4" t="n">
-        <v>58345</v>
+        <v>58348</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>440509</v>
+        <v>440494</v>
       </c>
       <c r="R4" t="n">
-        <v>6511915</v>
+        <v>6511873</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -949,12 +949,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-04-19</t>
+          <t>2023-04-20</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-04-19</t>
+          <t>2023-04-20</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123158430</v>
+        <v>123158425</v>
       </c>
       <c r="B5" t="n">
-        <v>56438</v>
+        <v>58348</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>208257</v>
+        <v>208250</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kopparödla</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Anguis fragilis</t>
+          <t>Rana arvalis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Nilsson, 1842</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>440506</v>
+        <v>440504</v>
       </c>
       <c r="R5" t="n">
-        <v>6511890</v>
+        <v>6511909</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123158428</v>
+        <v>123158443</v>
       </c>
       <c r="B6" t="n">
-        <v>58345</v>
+        <v>56449</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>208250</v>
+        <v>208255</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Skogsödla</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Zootoca vivipara</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
+          <t>(Jacquin, 1787)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>440508</v>
+        <v>440500</v>
       </c>
       <c r="R6" t="n">
-        <v>6511917</v>
+        <v>6511916</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1153,12 +1153,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2023-05-08</t>
+          <t>2023-04-19</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2023-05-08</t>
+          <t>2023-04-19</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123158461</v>
+        <v>123158431</v>
       </c>
       <c r="B7" t="n">
-        <v>58355</v>
+        <v>58348</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>208242</v>
+        <v>208250</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mindre vattensalamander</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lissotriton vulgaris</t>
+          <t>Rana arvalis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Nilsson, 1842</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>440479</v>
+        <v>440509</v>
       </c>
       <c r="R7" t="n">
-        <v>6511921</v>
+        <v>6511891</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1255,12 +1255,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2023-04-17</t>
+          <t>2023-05-08</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2023-04-17</t>
+          <t>2023-05-08</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123158448</v>
+        <v>123158445</v>
       </c>
       <c r="B8" t="n">
-        <v>58345</v>
+        <v>58348</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>440528</v>
+        <v>440506</v>
       </c>
       <c r="R8" t="n">
-        <v>6511918</v>
+        <v>6511913</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123158426</v>
+        <v>123158427</v>
       </c>
       <c r="B9" t="n">
-        <v>58345</v>
+        <v>58348</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1429,7 +1429,7 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>440498</v>
+        <v>440503</v>
       </c>
       <c r="R9" t="n">
         <v>6511919</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123158445</v>
+        <v>123158433</v>
       </c>
       <c r="B10" t="n">
-        <v>58345</v>
+        <v>58358</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1507,21 +1507,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>208250</v>
+        <v>208242</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Mindre vattensalamander</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Lissotriton vulgaris</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1534,7 +1534,7 @@
         <v>440506</v>
       </c>
       <c r="R10" t="n">
-        <v>6511913</v>
+        <v>6511891</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1561,12 +1561,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2023-04-19</t>
+          <t>2023-05-08</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2023-04-19</t>
+          <t>2023-05-08</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123158427</v>
+        <v>123158460</v>
       </c>
       <c r="B11" t="n">
-        <v>58345</v>
+        <v>58358</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1609,21 +1609,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>208250</v>
+        <v>208242</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Mindre vattensalamander</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Lissotriton vulgaris</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>440503</v>
+        <v>440478</v>
       </c>
       <c r="R11" t="n">
-        <v>6511919</v>
+        <v>6511923</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1663,12 +1663,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2023-05-08</t>
+          <t>2023-04-17</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2023-05-08</t>
+          <t>2023-04-17</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1695,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123158433</v>
+        <v>123158461</v>
       </c>
       <c r="B12" t="n">
-        <v>58355</v>
+        <v>58358</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1735,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>440506</v>
+        <v>440479</v>
       </c>
       <c r="R12" t="n">
-        <v>6511891</v>
+        <v>6511921</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1765,12 +1765,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2023-05-08</t>
+          <t>2023-04-17</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2023-05-08</t>
+          <t>2023-04-17</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1797,10 +1797,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123158440</v>
+        <v>123158452</v>
       </c>
       <c r="B13" t="n">
-        <v>58345</v>
+        <v>58348</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>440491</v>
+        <v>440487</v>
       </c>
       <c r="R13" t="n">
-        <v>6511891</v>
+        <v>6511899</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1899,10 +1899,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123158446</v>
+        <v>123158448</v>
       </c>
       <c r="B14" t="n">
-        <v>58345</v>
+        <v>58348</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1939,10 +1939,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>440510</v>
+        <v>440528</v>
       </c>
       <c r="R14" t="n">
-        <v>6511914</v>
+        <v>6511918</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2001,10 +2001,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123158431</v>
+        <v>123158424</v>
       </c>
       <c r="B15" t="n">
-        <v>58345</v>
+        <v>58322</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2017,21 +2017,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>208250</v>
+        <v>208245</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2041,10 +2041,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>440509</v>
+        <v>440481</v>
       </c>
       <c r="R15" t="n">
-        <v>6511891</v>
+        <v>6511927</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2103,10 +2103,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123158452</v>
+        <v>123158446</v>
       </c>
       <c r="B16" t="n">
-        <v>58345</v>
+        <v>58348</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2143,10 +2143,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>440487</v>
+        <v>440510</v>
       </c>
       <c r="R16" t="n">
-        <v>6511899</v>
+        <v>6511914</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2205,10 +2205,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123158443</v>
+        <v>123158430</v>
       </c>
       <c r="B17" t="n">
-        <v>56446</v>
+        <v>56441</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2221,21 +2221,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>208255</v>
+        <v>208257</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skogsödla</t>
+          <t>Kopparödla</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Zootoca vivipara</t>
+          <t>Anguis fragilis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Jacquin, 1787)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2245,10 +2245,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>440500</v>
+        <v>440506</v>
       </c>
       <c r="R17" t="n">
-        <v>6511916</v>
+        <v>6511890</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2275,12 +2275,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2023-04-19</t>
+          <t>2023-05-08</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2023-04-19</t>
+          <t>2023-05-08</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2307,10 +2307,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123158451</v>
+        <v>123158440</v>
       </c>
       <c r="B18" t="n">
-        <v>58345</v>
+        <v>58348</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2347,10 +2347,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>440494</v>
+        <v>440491</v>
       </c>
       <c r="R18" t="n">
-        <v>6511873</v>
+        <v>6511891</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2377,12 +2377,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2023-04-20</t>
+          <t>2023-04-19</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2023-04-20</t>
+          <t>2023-04-19</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2409,10 +2409,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123158425</v>
+        <v>123158441</v>
       </c>
       <c r="B19" t="n">
-        <v>58345</v>
+        <v>58348</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2449,10 +2449,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>440504</v>
+        <v>440509</v>
       </c>
       <c r="R19" t="n">
-        <v>6511909</v>
+        <v>6511915</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2479,12 +2479,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2023-05-08</t>
+          <t>2023-04-19</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2023-05-08</t>
+          <t>2023-04-19</t>
         </is>
       </c>
       <c r="AD19" t="b">

--- a/artfynd/A 46932-2020 artfynd.xlsx
+++ b/artfynd/A 46932-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123158426</v>
+        <v>123158445</v>
       </c>
       <c r="B2" t="n">
-        <v>58348</v>
+        <v>58349</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>440498</v>
+        <v>440506</v>
       </c>
       <c r="R2" t="n">
-        <v>6511919</v>
+        <v>6511913</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -745,12 +745,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-05-08</t>
+          <t>2023-04-19</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-05-08</t>
+          <t>2023-04-19</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123158428</v>
+        <v>123158433</v>
       </c>
       <c r="B3" t="n">
-        <v>58348</v>
+        <v>58359</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>208250</v>
+        <v>208242</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Mindre vattensalamander</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Lissotriton vulgaris</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>440508</v>
+        <v>440506</v>
       </c>
       <c r="R3" t="n">
-        <v>6511917</v>
+        <v>6511891</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123158451</v>
+        <v>123158441</v>
       </c>
       <c r="B4" t="n">
-        <v>58348</v>
+        <v>58349</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>440494</v>
+        <v>440509</v>
       </c>
       <c r="R4" t="n">
-        <v>6511873</v>
+        <v>6511915</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -949,12 +949,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-04-20</t>
+          <t>2023-04-19</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-04-20</t>
+          <t>2023-04-19</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123158425</v>
+        <v>123158427</v>
       </c>
       <c r="B5" t="n">
-        <v>58348</v>
+        <v>58349</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>440504</v>
+        <v>440503</v>
       </c>
       <c r="R5" t="n">
-        <v>6511909</v>
+        <v>6511919</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123158443</v>
+        <v>123158461</v>
       </c>
       <c r="B6" t="n">
-        <v>56449</v>
+        <v>58359</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>208255</v>
+        <v>208242</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skogsödla</t>
+          <t>Mindre vattensalamander</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Zootoca vivipara</t>
+          <t>Lissotriton vulgaris</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Jacquin, 1787)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>440500</v>
+        <v>440479</v>
       </c>
       <c r="R6" t="n">
-        <v>6511916</v>
+        <v>6511921</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1153,12 +1153,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2023-04-19</t>
+          <t>2023-04-17</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2023-04-19</t>
+          <t>2023-04-17</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123158431</v>
+        <v>123158428</v>
       </c>
       <c r="B7" t="n">
-        <v>58348</v>
+        <v>58349</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>440509</v>
+        <v>440508</v>
       </c>
       <c r="R7" t="n">
-        <v>6511891</v>
+        <v>6511917</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123158445</v>
+        <v>123158448</v>
       </c>
       <c r="B8" t="n">
-        <v>58348</v>
+        <v>58349</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>440506</v>
+        <v>440528</v>
       </c>
       <c r="R8" t="n">
-        <v>6511913</v>
+        <v>6511918</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123158427</v>
+        <v>123158451</v>
       </c>
       <c r="B9" t="n">
-        <v>58348</v>
+        <v>58349</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>440503</v>
+        <v>440494</v>
       </c>
       <c r="R9" t="n">
-        <v>6511919</v>
+        <v>6511873</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1459,12 +1459,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2023-05-08</t>
+          <t>2023-04-20</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2023-05-08</t>
+          <t>2023-04-20</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123158433</v>
+        <v>123158446</v>
       </c>
       <c r="B10" t="n">
-        <v>58358</v>
+        <v>58349</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1507,21 +1507,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>208242</v>
+        <v>208250</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mindre vattensalamander</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lissotriton vulgaris</t>
+          <t>Rana arvalis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Nilsson, 1842</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>440506</v>
+        <v>440510</v>
       </c>
       <c r="R10" t="n">
-        <v>6511891</v>
+        <v>6511914</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1561,12 +1561,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2023-05-08</t>
+          <t>2023-04-19</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2023-05-08</t>
+          <t>2023-04-19</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123158460</v>
+        <v>123158431</v>
       </c>
       <c r="B11" t="n">
-        <v>58358</v>
+        <v>58349</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1609,21 +1609,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>208242</v>
+        <v>208250</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mindre vattensalamander</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lissotriton vulgaris</t>
+          <t>Rana arvalis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Nilsson, 1842</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>440478</v>
+        <v>440509</v>
       </c>
       <c r="R11" t="n">
-        <v>6511923</v>
+        <v>6511891</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1663,12 +1663,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2023-04-17</t>
+          <t>2023-05-08</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2023-04-17</t>
+          <t>2023-05-08</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1695,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123158461</v>
+        <v>123158426</v>
       </c>
       <c r="B12" t="n">
-        <v>58358</v>
+        <v>58349</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1711,21 +1711,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>208242</v>
+        <v>208250</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mindre vattensalamander</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lissotriton vulgaris</t>
+          <t>Rana arvalis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Nilsson, 1842</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1735,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>440479</v>
+        <v>440498</v>
       </c>
       <c r="R12" t="n">
-        <v>6511921</v>
+        <v>6511919</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1765,12 +1765,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2023-04-17</t>
+          <t>2023-05-08</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2023-04-17</t>
+          <t>2023-05-08</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1797,10 +1797,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123158452</v>
+        <v>123158443</v>
       </c>
       <c r="B13" t="n">
-        <v>58348</v>
+        <v>56449</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1813,21 +1813,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>208250</v>
+        <v>208255</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Skogsödla</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Zootoca vivipara</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
+          <t>(Jacquin, 1787)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>440487</v>
+        <v>440500</v>
       </c>
       <c r="R13" t="n">
-        <v>6511899</v>
+        <v>6511916</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1899,10 +1899,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123158448</v>
+        <v>123158452</v>
       </c>
       <c r="B14" t="n">
-        <v>58348</v>
+        <v>58349</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1939,10 +1939,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>440528</v>
+        <v>440487</v>
       </c>
       <c r="R14" t="n">
-        <v>6511918</v>
+        <v>6511899</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2001,10 +2001,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123158424</v>
+        <v>123158430</v>
       </c>
       <c r="B15" t="n">
-        <v>58322</v>
+        <v>56441</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2017,21 +2017,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>208245</v>
+        <v>208257</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Kopparödla</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Anguis fragilis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2041,10 +2041,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>440481</v>
+        <v>440506</v>
       </c>
       <c r="R15" t="n">
-        <v>6511927</v>
+        <v>6511890</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2103,10 +2103,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123158446</v>
+        <v>123158460</v>
       </c>
       <c r="B16" t="n">
-        <v>58348</v>
+        <v>58359</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2119,21 +2119,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>208250</v>
+        <v>208242</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Mindre vattensalamander</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Lissotriton vulgaris</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2143,10 +2143,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>440510</v>
+        <v>440478</v>
       </c>
       <c r="R16" t="n">
-        <v>6511914</v>
+        <v>6511923</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2173,12 +2173,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2023-04-19</t>
+          <t>2023-04-17</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2023-04-19</t>
+          <t>2023-04-17</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2205,10 +2205,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123158430</v>
+        <v>123158424</v>
       </c>
       <c r="B17" t="n">
-        <v>56441</v>
+        <v>58323</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2221,21 +2221,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>208257</v>
+        <v>208245</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kopparödla</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Anguis fragilis</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2245,10 +2245,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>440506</v>
+        <v>440481</v>
       </c>
       <c r="R17" t="n">
-        <v>6511890</v>
+        <v>6511927</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2310,7 +2310,7 @@
         <v>123158440</v>
       </c>
       <c r="B18" t="n">
-        <v>58348</v>
+        <v>58349</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2409,10 +2409,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123158441</v>
+        <v>123158425</v>
       </c>
       <c r="B19" t="n">
-        <v>58348</v>
+        <v>58349</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2449,10 +2449,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>440509</v>
+        <v>440504</v>
       </c>
       <c r="R19" t="n">
-        <v>6511915</v>
+        <v>6511909</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2479,12 +2479,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2023-04-19</t>
+          <t>2023-05-08</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2023-04-19</t>
+          <t>2023-05-08</t>
         </is>
       </c>
       <c r="AD19" t="b">

--- a/artfynd/A 46932-2020 artfynd.xlsx
+++ b/artfynd/A 46932-2020 artfynd.xlsx
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123158461</v>
+        <v>123158448</v>
       </c>
       <c r="B6" t="n">
-        <v>58359</v>
+        <v>58349</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>208242</v>
+        <v>208250</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mindre vattensalamander</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lissotriton vulgaris</t>
+          <t>Rana arvalis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Nilsson, 1842</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>440479</v>
+        <v>440528</v>
       </c>
       <c r="R6" t="n">
-        <v>6511921</v>
+        <v>6511918</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1153,12 +1153,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2023-04-17</t>
+          <t>2023-04-19</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2023-04-17</t>
+          <t>2023-04-19</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123158428</v>
+        <v>123158461</v>
       </c>
       <c r="B7" t="n">
-        <v>58349</v>
+        <v>58359</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>208250</v>
+        <v>208242</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Mindre vattensalamander</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Lissotriton vulgaris</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>440508</v>
+        <v>440479</v>
       </c>
       <c r="R7" t="n">
-        <v>6511917</v>
+        <v>6511921</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1255,12 +1255,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2023-05-08</t>
+          <t>2023-04-17</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2023-05-08</t>
+          <t>2023-04-17</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1287,7 +1287,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123158448</v>
+        <v>123158428</v>
       </c>
       <c r="B8" t="n">
         <v>58349</v>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>440528</v>
+        <v>440508</v>
       </c>
       <c r="R8" t="n">
-        <v>6511918</v>
+        <v>6511917</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1357,12 +1357,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2023-04-19</t>
+          <t>2023-05-08</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2023-04-19</t>
+          <t>2023-05-08</t>
         </is>
       </c>
       <c r="AD8" t="b">
